--- a/playground/data/demo.xlsx
+++ b/playground/data/demo.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Sheet JS" sheetId="1" r:id="rId1"/>
+    <sheet name="users" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -64,8 +64,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -397,67 +398,149 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:G6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>This</v>
+        <v>userId</v>
       </c>
       <c r="B1" t="str">
-        <v>is</v>
+        <v>username</v>
       </c>
       <c r="C1" t="str">
-        <v>a</v>
+        <v>email</v>
       </c>
       <c r="D1" t="str">
-        <v>Test</v>
+        <v>avatar</v>
+      </c>
+      <c r="E1" t="str">
+        <v>password</v>
+      </c>
+      <c r="F1" t="str">
+        <v>birthdate</v>
+      </c>
+      <c r="G1" t="str">
+        <v>registeredAt</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>வணக்கம்</v>
+        <v>b15faeed-a812-42d7-9c69-230320d1df99</v>
       </c>
       <c r="B2" t="str">
-        <v>สวัสดี</v>
+        <v>Sasha90</v>
       </c>
       <c r="C2" t="str">
-        <v>你好</v>
+        <v>Mackenzie74@hotmail.com</v>
       </c>
       <c r="D2" t="str">
-        <v>가지마</v>
+        <v>https://cdn.jsdelivr.net/gh/faker-js/assets-person-portrait/male/512/92.jpg</v>
+      </c>
+      <c r="E2" t="str">
+        <v>JpOzhDijQlbc2lY</v>
+      </c>
+      <c r="F2" s="1">
+        <v>29702.76482326389</v>
+      </c>
+      <c r="G2" s="1">
+        <v>45740.415507314814</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>3</v>
-      </c>
-      <c r="D3">
-        <v>4</v>
+      <c r="A3" t="str">
+        <v>cfe82e32-ce34-438c-9112-74dbcfcbe8b6</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Gisselle.Pouros65</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Lawrence43@hotmail.com</v>
+      </c>
+      <c r="D3" t="str">
+        <v>https://avatars.githubusercontent.com/u/32111644</v>
+      </c>
+      <c r="E3" t="str">
+        <v>rn2RKFPd5mtqzK1</v>
+      </c>
+      <c r="F3" s="1">
+        <v>16624.177784224536</v>
+      </c>
+      <c r="G3" s="1">
+        <v>45824.11849894676</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Click</v>
+        <v>13ebc154-6afd-4d33-97ad-c071dadf1a8c</v>
       </c>
       <c r="B4" t="str">
-        <v>to</v>
+        <v>Norbert.Cassin43</v>
       </c>
       <c r="C4" t="str">
-        <v>edit</v>
+        <v>Nickolas62@gmail.com</v>
       </c>
       <c r="D4" t="str">
-        <v>cells</v>
+        <v>https://avatars.githubusercontent.com/u/74982450</v>
+      </c>
+      <c r="E4" t="str">
+        <v>gnIOvK462ZmuW1U</v>
+      </c>
+      <c r="F4" s="1">
+        <v>30397.109063020835</v>
+      </c>
+      <c r="G4" s="1">
+        <v>45961.93309982639</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>53457b42-18fe-46cc-af2a-32a0772373d8</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Edwina71</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Amelia16@hotmail.com</v>
+      </c>
+      <c r="D5" t="str">
+        <v>https://cdn.jsdelivr.net/gh/faker-js/assets-person-portrait/male/512/67.jpg</v>
+      </c>
+      <c r="E5" t="str">
+        <v>XDvsmKeUDVecCNt</v>
+      </c>
+      <c r="F5" s="1">
+        <v>31086.318099074073</v>
+      </c>
+      <c r="G5" s="1">
+        <v>45888.653315625</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>dc215c62-6fda-41ff-8c9f-d287b9d69ee5</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Lupe.Dooley42</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Aiyana.Schuppe@yahoo.com</v>
+      </c>
+      <c r="D6" t="str">
+        <v>https://cdn.jsdelivr.net/gh/faker-js/assets-person-portrait/male/512/1.jpg</v>
+      </c>
+      <c r="E6" t="str">
+        <v>HQe_6vXkpMs2VPx</v>
+      </c>
+      <c r="F6" s="1">
+        <v>30768.446070949074</v>
+      </c>
+      <c r="G6" s="1">
+        <v>45794.85911724537</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G6"/>
   </ignoredErrors>
 </worksheet>
 </file>